--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488010_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488010_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3686</v>
+        <v>3.3572</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8732</v>
+        <v>3.8337</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5046</v>
+        <v>-0.4765</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4752</v>
@@ -610,13 +610,13 @@
         <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0165</v>
+        <v>-1.0279</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3706</v>
+        <v>-0.4101</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6459</v>
+        <v>-0.6179</v>
       </c>
       <c r="V2" t="n">
         <v>2.4816</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7634</v>
+        <v>1.8267</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0555</v>
+        <v>0.1483</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8189</v>
+        <v>1.6785</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3823</v>
@@ -688,13 +688,13 @@
         <v>2.9733</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7948</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7488</v>
+        <v>-0.545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.046</v>
+        <v>-0.1864</v>
       </c>
       <c r="V3" t="n">
         <v>2.1476</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9219000000000001</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3598</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5621</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.84</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6575</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1825</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7391</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.06</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6791</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1009</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5975</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5034</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5479</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8077</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7402</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2734</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.139</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.1301</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6052999999999999</v>
+        <v>-1.0908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.4803</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.0172</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4508</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.5664</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.108</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.9312</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1768</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.9004</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.4202</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.4801</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0545</v>
+        <v>-0.0544</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.2514</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0102</v>
+        <v>0.197</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0908</v>
+        <v>-1.84</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4803</v>
+        <v>-0.6575</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.1825</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0172</v>
+        <v>-0.7391</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4508</v>
+        <v>-0.06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5664</v>
+        <v>-0.6791</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.108</v>
+        <v>-1.1009</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9312</v>
+        <v>-0.5975</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1768</v>
+        <v>-0.5034</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R6" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9637</v>
+        <v>0.5717</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.624</v>
+        <v>0.1965</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3397</v>
+        <v>0.3752</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2071</v>
+        <v>2.0068</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5331</v>
+        <v>2.2734</v>
       </c>
       <c r="X6" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>J. LUQUE GOMEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8823</v>
+        <v>-1.611</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3452</v>
+        <v>-0.8645</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5371</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6881</v>
+        <v>-3.3381</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8863</v>
+        <v>-4.2259</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5744</v>
+        <v>0.8878</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06710000000000001</v>
+        <v>-0.2737</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0133</v>
+        <v>-2.6156</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0804</v>
+        <v>2.342</v>
       </c>
       <c r="M7" t="n">
-        <v>0.621</v>
+        <v>-3.0645</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8731</v>
+        <v>-1.6103</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4941</v>
+        <v>-1.4542</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5858</v>
+        <v>2.3787</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9733</v>
+        <v>-0.1982</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3811</v>
+        <v>-0.4524</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2496</v>
+        <v>-0.3927</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1315</v>
+        <v>-0.0597</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>-0.1992</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4142</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2867</v>
+        <v>-1.7243</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4247</v>
+        <v>-1.2433</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1381</v>
+        <v>-0.4809</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1509</v>
+        <v>0.6881</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5138</v>
+        <v>-0.8863</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6647</v>
+        <v>1.5744</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0284</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9843</v>
+        <v>-0.0133</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0441</v>
+        <v>0.0804</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.1793</v>
+        <v>0.621</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4705</v>
+        <v>-0.8731</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7087</v>
+        <v>1.4941</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9822</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.1538</v>
+        <v>-2.9733</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1716</v>
+        <v>1.3876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.765</v>
+        <v>-0.223</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5064</v>
+        <v>-0.1477</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2586</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>1.6115</v>
+        <v>-0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2071</v>
+        <v>1.8107</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4044</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LUQUE GOMEZ</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3336</v>
+        <v>-2.4384</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3344</v>
+        <v>-2.4642</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9992</v>
+        <v>0.0257</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.3381</v>
+        <v>-1.1509</v>
       </c>
       <c r="H9" t="n">
-        <v>-4.2259</v>
+        <v>0.5138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8878</v>
+        <v>-1.6647</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2737</v>
+        <v>2.0284</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.6156</v>
+        <v>1.9843</v>
       </c>
       <c r="L9" t="n">
-        <v>2.342</v>
+        <v>0.0441</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0645</v>
+        <v>-3.1793</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6103</v>
+        <v>-1.4705</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4542</v>
+        <v>-1.7087</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3787</v>
+        <v>-1.9822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1982</v>
+        <v>-5.1538</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5769</v>
+        <v>3.1716</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.175</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8625</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3124</v>
+        <v>-0.3709</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1992</v>
+        <v>1.6115</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1992</v>
+        <v>0.4044</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2048</v>
+        <v>-2.6964</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2537</v>
+        <v>0.6217</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4584</v>
+        <v>-3.318</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7872</v>
@@ -1234,13 +1234,13 @@
         <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0202</v>
+        <v>0.4882</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1762</v>
+        <v>0.1918</v>
       </c>
       <c r="U10" t="n">
-        <v>0.156</v>
+        <v>0.2964</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8027</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4064</v>
+        <v>-5.4873</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1012</v>
+        <v>-2.4068</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3052</v>
+        <v>-3.0806</v>
       </c>
       <c r="G11" t="n">
         <v>-4.4542</v>
@@ -1312,13 +1312,13 @@
         <v>2.5769</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6856</v>
+        <v>-1.7666</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.132</v>
+        <v>-0.4376</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5536</v>
+        <v>-1.329</v>
       </c>
       <c r="V11" t="n">
         <v>0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.1281</v>
+        <v>-10.1114</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.715</v>
+        <v>-6.7545</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4131</v>
+        <v>-3.3569</v>
       </c>
       <c r="G12" t="n">
         <v>-8.202299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>3.3698</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5462</v>
+        <v>-0.5295</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4954</v>
+        <v>-0.5349</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0508</v>
+        <v>0.0053</v>
       </c>
       <c r="V12" t="n">
         <v>0.4044</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.6372</v>
+        <v>-18.3251</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.948700000000001</v>
+        <v>-8.636700000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-9.6883</v>
@@ -1441,13 +1441,13 @@
         <v>-10.581</v>
       </c>
       <c r="J13" t="n">
-        <v>2.397399999999999</v>
+        <v>2.3974</v>
       </c>
       <c r="K13" t="n">
         <v>1.860699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5367999999999995</v>
+        <v>0.5368000000000004</v>
       </c>
       <c r="M13" t="n">
         <v>-23.825</v>
@@ -1468,13 +1468,13 @@
         <v>22.7956</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.800199999999999</v>
+        <v>-5.4881</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3578</v>
+        <v>-3.0458</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4423</v>
+        <v>-2.4424</v>
       </c>
       <c r="V13" t="n">
         <v>8.5905</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.3154</v>
+        <v>10.9473</v>
       </c>
       <c r="E14" t="n">
-        <v>8.2971</v>
+        <v>7.1991</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0182</v>
+        <v>3.7482</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1378</v>
+        <v>8.7963</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6418</v>
+        <v>0.3626</v>
       </c>
       <c r="I14" t="n">
-        <v>4.496</v>
+        <v>8.4337</v>
       </c>
       <c r="J14" t="n">
-        <v>7.1028</v>
+        <v>7.8805</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1615</v>
+        <v>-0.1343</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9413</v>
+        <v>8.014799999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.035</v>
+        <v>0.9159</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5198</v>
+        <v>0.497</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5547</v>
+        <v>0.4189</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>3.568</v>
+        <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9882</v>
+        <v>0.6158</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4957</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4925</v>
+        <v>0.522</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6036</v>
+        <v>0.9405</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6808</v>
+        <v>1.2071</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.0772</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.4839</v>
+        <v>10.5752</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1804</v>
+        <v>8.5009</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3035</v>
+        <v>2.0744</v>
       </c>
       <c r="G15" t="n">
-        <v>8.7963</v>
+        <v>7.1378</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3626</v>
+        <v>2.6418</v>
       </c>
       <c r="I15" t="n">
-        <v>8.4337</v>
+        <v>4.496</v>
       </c>
       <c r="J15" t="n">
-        <v>7.8805</v>
+        <v>7.1028</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1343</v>
+        <v>3.1615</v>
       </c>
       <c r="L15" t="n">
-        <v>8.014799999999999</v>
+        <v>3.9413</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9159</v>
+        <v>0.035</v>
       </c>
       <c r="N15" t="n">
-        <v>0.497</v>
+        <v>-0.5198</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4189</v>
+        <v>0.5547</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5769</v>
+        <v>3.568</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8476</v>
+        <v>1.2481</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9249000000000001</v>
+        <v>0.6995</v>
       </c>
       <c r="U15" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.5486</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9405</v>
+        <v>0.6036</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>2.6808</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2666</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9163</v>
+        <v>5.1795</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4599</v>
+        <v>1.6263</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4563</v>
+        <v>3.5533</v>
       </c>
       <c r="G16" t="n">
         <v>4.0827</v>
@@ -1702,13 +1702,13 @@
         <v>3.568</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6374</v>
+        <v>1.9006</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6507</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9867</v>
+        <v>1.0836</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4074</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.482</v>
+        <v>1.5838</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9663</v>
+        <v>1.0682</v>
       </c>
       <c r="F17" t="n">
         <v>0.5157</v>
@@ -1780,10 +1780,10 @@
         <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1138</v>
+        <v>0.2156</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0624</v>
+        <v>0.0395</v>
       </c>
       <c r="U17" t="n">
         <v>0.1762</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3464</v>
+        <v>0.5782</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6579</v>
+        <v>-0.4541</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0043</v>
+        <v>1.0323</v>
       </c>
       <c r="G18" t="n">
         <v>0.4239</v>
@@ -1858,13 +1858,13 @@
         <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0701</v>
+        <v>0.3019</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1248</v>
+        <v>0.0789</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1949</v>
+        <v>0.223</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9405</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1904</v>
+        <v>0.0447</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8506</v>
+        <v>-2.9524</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6602</v>
+        <v>2.9971</v>
       </c>
       <c r="G19" t="n">
         <v>1.2978</v>
@@ -1936,13 +1936,13 @@
         <v>3.3698</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3642</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3085</v>
+        <v>0.2067</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0557</v>
+        <v>0.3927</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2666</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3588</v>
+        <v>-2.3353</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0867</v>
+        <v>0.068</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4456</v>
+        <v>-2.4033</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8676</v>
@@ -2014,13 +2014,13 @@
         <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0283</v>
+        <v>1.0518</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9054</v>
+        <v>0.8867</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1229</v>
+        <v>0.1651</v>
       </c>
       <c r="V20" t="n">
         <v>0.4627</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MALAVE FERNANDEZ</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4175</v>
+        <v>-2.8106</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4975</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-1.9331</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4568</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3144</v>
+        <v>-0.7869</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2908</v>
+        <v>1.2437</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7877999999999999</v>
+        <v>1.5708</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1009</v>
+        <v>-0.3292</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6869</v>
+        <v>1.9</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1825</v>
+        <v>-1.1141</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2136</v>
+        <v>-0.4577</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3961</v>
+        <v>-0.6563</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3787</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1704</v>
+        <v>-0.0514</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.312</v>
+        <v>-0.4661</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1416</v>
+        <v>0.4147</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4737</v>
+        <v>-3.0178</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>-3.0178</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>D. MALAVE FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4427</v>
+        <v>-3.0883</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.285</v>
+        <v>-2.1919</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1577</v>
+        <v>-0.8964</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4568</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7869</v>
+        <v>0.3144</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2437</v>
+        <v>0.2908</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5708</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3292</v>
+        <v>0.1009</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9</v>
+        <v>0.6869</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1141</v>
+        <v>-0.1825</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4577</v>
+        <v>0.2136</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6563</v>
+        <v>-0.3961</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1982</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6835</v>
+        <v>0.1588</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8736</v>
+        <v>-0.0064</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1901</v>
+        <v>0.1651</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.0178</v>
+        <v>-1.4737</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.0178</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6607</v>
+        <v>-4.107</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7035</v>
+        <v>-2.3979</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9572</v>
+        <v>-1.7091</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8045</v>
@@ -2248,13 +2248,13 @@
         <v>1.1893</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1704</v>
+        <v>0.7241</v>
       </c>
       <c r="T23" t="n">
-        <v>0.191</v>
+        <v>0.4966</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0206</v>
+        <v>0.2275</v>
       </c>
       <c r="V23" t="n">
         <v>-4.2249</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.4739</v>
+        <v>16.5675</v>
       </c>
       <c r="E24" t="n">
-        <v>9.995900000000001</v>
+        <v>9.588700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>6.477799999999998</v>
+        <v>6.9791</v>
       </c>
       <c r="G24" t="n">
         <v>21.1686</v>
@@ -2314,10 +2314,10 @@
         <v>-1.6048</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5479000000000002</v>
+        <v>-0.5478999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.775</v>
+        <v>-2.774999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-22.7956</v>
@@ -2326,13 +2326,13 @@
         <v>20.0205</v>
       </c>
       <c r="S24" t="n">
-        <v>6.6709</v>
+        <v>6.764600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2536</v>
+        <v>2.8462</v>
       </c>
       <c r="U24" t="n">
-        <v>3.4173</v>
+        <v>3.9185</v>
       </c>
       <c r="V24" t="n">
         <v>-8.5907</v>
